--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_5_14.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/400000/Output_5_14.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>319018.5656753904</v>
+        <v>315790.7458131064</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547406</v>
+        <v>3001330.373596265</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745724</v>
+        <v>20361635.87782002</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4814095.689442963</v>
+        <v>4805772.747885407</v>
       </c>
     </row>
     <row r="11">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -1141,10 +1141,10 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9608114308426619</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1183,10 +1183,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22.54368386855027</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -1369,16 +1369,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>22.90079999999999</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="G11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1451,13 +1451,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1493,16 +1493,16 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W12" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2741920426674311</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12.91010078545518</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1609,13 +1609,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1639,10 +1639,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1688,10 +1688,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1733,13 +1733,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X15" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -1764,22 +1764,22 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1797,22 +1797,22 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
@@ -1834,28 +1834,28 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.361305680129117</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1958,19 +1958,19 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>24.66239999999999</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>22.02246762618611</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2034,19 +2034,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2068,19 +2068,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2147,25 +2147,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>129.9689980595289</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2201,22 +2201,22 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>34.66067414728059</v>
       </c>
     </row>
     <row r="22">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2368,13 +2368,13 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2387,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>104.6829309709404</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>200.1647286948216</v>
@@ -2444,16 +2444,16 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>130.0843554087448</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -2472,13 +2472,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>47.02492433367362</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200.3235106453875</v>
+        <v>40.47627913313517</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2587,10 +2587,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2602,13 +2602,13 @@
         <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2621,31 +2621,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>62.82598119855365</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2675,19 +2675,19 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>29.05241763862484</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
@@ -2760,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2779,13 +2779,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -2839,16 +2839,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>35.46543116184174</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
         <v>172.7084989883157</v>
@@ -2867,16 +2867,16 @@
         <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -2918,13 +2918,13 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.107638666203086</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
         <v>0</v>
@@ -2964,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2994,7 +2994,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>24.75543250779077</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3006,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
     </row>
     <row r="32">
@@ -3019,10 +3019,10 @@
         <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>70.34400780127524</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -3031,10 +3031,10 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3064,28 +3064,28 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>179.3813007854552</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3095,7 +3095,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>26.1692523664268</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0.7465913262578567</v>
@@ -3143,25 +3143,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
         <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>215</v>
+        <v>63.24215619956617</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
@@ -3222,7 +3222,7 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3237,7 +3237,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -3268,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3298,19 +3298,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>196.0929612559941</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -3319,10 +3319,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>29.51218284430547</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="Y35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3332,19 +3332,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>41.34999770271885</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3383,19 +3383,19 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>204.2072713051783</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3414,25 +3414,25 @@
         <v>0</v>
       </c>
       <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3493,16 +3493,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>189.3719999999999</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3511,10 +3511,10 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3553,13 +3553,13 @@
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X38" t="n">
-        <v>215</v>
+        <v>182.6878519172211</v>
       </c>
       <c r="Y38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3572,16 +3572,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -3617,28 +3617,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>112.8753346539135</v>
       </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>36.23314791538029</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3699,13 +3699,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,13 +3727,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="C41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="D41" t="n">
-        <v>177.6197007854553</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3775,7 +3775,7 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>213</v>
+        <v>31.07264828539811</v>
       </c>
     </row>
     <row r="42">
@@ -3806,19 +3806,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>126.8720801868694</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>51.67155945914826</v>
       </c>
       <c r="G42" t="n">
         <v>137.3435171632106</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3866,10 +3866,10 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>15.12050584389412</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>15.12050584389412</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>15.12050584389412</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>15.12050584389412</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>14.14998924708335</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>93.90838463177292</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>67.64575836914665</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>41.38313210652039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.2121212121212</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>27.82</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>53.56</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>79.3</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>51.47474747474747</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.96597589035326</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>54.96597589035326</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>54.96597589035326</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>54.96597589035326</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>54.96597589035326</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>54.96597589035326</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>54.96597589035326</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>28.70334962772699</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2.44072336510073</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28.18072336510073</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.92072336510073</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>79.66072336510072</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>77.73737373737373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F11" t="n">
-        <v>80.86787878787879</v>
+        <v>79.68686933990632</v>
       </c>
       <c r="G11" t="n">
-        <v>54.60525252525252</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="H11" t="n">
-        <v>28.34262626262626</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M11" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C12" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D12" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E12" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F12" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G12" t="n">
-        <v>54.60525252525252</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H12" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L12" t="n">
-        <v>53.56</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="M12" t="n">
-        <v>78.26000000000001</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="N12" t="n">
-        <v>78.26000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="O12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U12" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V12" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="W12" t="n">
-        <v>80.86787878787879</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="X12" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y12" t="n">
-        <v>80.86787878787879</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="C13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="D13" t="n">
-        <v>103.6392766348993</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E13" t="n">
-        <v>103.6392766348993</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="F13" t="n">
-        <v>77.37665037227302</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="G13" t="n">
-        <v>51.11402410964676</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="H13" t="n">
-        <v>24.85139784702049</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="I13" t="n">
-        <v>24.85139784702049</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="J13" t="n">
-        <v>24.57443618776046</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K13" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.3</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>103.6392766348993</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="R13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y13" t="n">
-        <v>103.6392766348993</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.34262626262626</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="C14" t="n">
-        <v>2.08</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="D14" t="n">
-        <v>2.08</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L14" t="n">
-        <v>2.08</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M14" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N14" t="n">
-        <v>53.56</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>93.90838463177292</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R14" t="n">
-        <v>67.64575836914665</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S14" t="n">
-        <v>67.64575836914665</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="T14" t="n">
-        <v>67.64575836914665</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="U14" t="n">
-        <v>41.38313210652039</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V14" t="n">
-        <v>41.38313210652039</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W14" t="n">
-        <v>41.38313210652039</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X14" t="n">
-        <v>41.38313210652039</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y14" t="n">
-        <v>41.38313210652039</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C15" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D15" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="E15" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>2.08</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>27.82</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="M15" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N15" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S15" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T15" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U15" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V15" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W15" t="n">
-        <v>25.2121212121212</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X15" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F16" t="n">
-        <v>103.72303834074</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G16" t="n">
-        <v>77.46041207811371</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H16" t="n">
-        <v>51.19778581548745</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I16" t="n">
-        <v>24.93515955286119</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="C17" t="n">
-        <v>87.08848484848485</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="D17" t="n">
-        <v>58.80565656565657</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="E17" t="n">
-        <v>30.52282828282829</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="F17" t="n">
-        <v>30.52282828282829</v>
+        <v>97.8833284203818</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="L17" t="n">
-        <v>28.84</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M17" t="n">
-        <v>56.56</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="V17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="W17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="X17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
       <c r="Y17" t="n">
-        <v>112</v>
+        <v>100.2684856730375</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="C18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="D18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="E18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>29.96</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>57.68</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>85.40000000000001</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>112</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="O18" t="n">
-        <v>112</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="P18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>87.08848484848485</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>58.80565656565657</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="U18" t="n">
-        <v>30.52282828282829</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="V18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="W18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="X18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.24</v>
+        <v>26.7539638887914</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24.48491679412739</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="C19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="D19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="E19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="F19" t="n">
-        <v>24.48491679412739</v>
+        <v>52.75142891054807</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>24.88271652639035</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>81.05057335978395</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>81.05057335978395</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="T19" t="n">
-        <v>81.05057335978395</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="U19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="V19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="W19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="X19" t="n">
-        <v>52.76774507695567</v>
+        <v>80.62014129470579</v>
       </c>
       <c r="Y19" t="n">
-        <v>24.48491679412739</v>
+        <v>80.62014129470579</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>720.5656565656566</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C20" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D20" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E20" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X20" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y20" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>552.3503195455885</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C21" t="n">
-        <v>552.3503195455885</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D21" t="n">
-        <v>403.4159098843372</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E21" t="n">
-        <v>403.4159098843372</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F21" t="n">
-        <v>272.1340936625909</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G21" t="n">
-        <v>133.4032682452064</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M21" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N21" t="n">
-        <v>851.7806659261865</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O21" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U21" t="n">
-        <v>964</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V21" t="n">
-        <v>964</v>
+        <v>298.4948343740486</v>
       </c>
       <c r="W21" t="n">
-        <v>720.5656565656566</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="X21" t="n">
-        <v>720.5656565656566</v>
+        <v>55.04605772994853</v>
       </c>
       <c r="Y21" t="n">
-        <v>720.5656565656566</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>467.0396977630861</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C23" t="n">
-        <v>223.6053543287427</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D23" t="n">
-        <v>223.6053543287427</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="E23" t="n">
-        <v>223.6053543287427</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F23" t="n">
-        <v>223.6053543287427</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V23" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="W23" t="n">
-        <v>953.9083846317729</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X23" t="n">
-        <v>953.9083846317729</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y23" t="n">
-        <v>710.4740411974295</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>125.0203343140812</v>
+        <v>194.4883050441255</v>
       </c>
       <c r="C24" t="n">
-        <v>125.0203343140812</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D24" t="n">
-        <v>125.0203343140812</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E24" t="n">
-        <v>125.0203343140812</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F24" t="n">
-        <v>125.0203343140812</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>487.8331058683492</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N24" t="n">
-        <v>726.4231058683491</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="O24" t="n">
-        <v>964</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>588.3960608094349</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U24" t="n">
-        <v>360.1724425458239</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="V24" t="n">
-        <v>125.0203343140812</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="W24" t="n">
-        <v>125.0203343140812</v>
+        <v>533.6469426057913</v>
       </c>
       <c r="X24" t="n">
-        <v>125.0203343140812</v>
+        <v>402.2486038090794</v>
       </c>
       <c r="Y24" t="n">
-        <v>125.0203343140812</v>
+        <v>194.4883050441255</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E25" t="n">
-        <v>66.7799235693673</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F25" t="n">
-        <v>66.7799235693673</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>274.7843326814268</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="C26" t="n">
-        <v>274.7843326814268</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="D26" t="n">
-        <v>274.7843326814268</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="E26" t="n">
-        <v>274.7843326814268</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="F26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I26" t="n">
-        <v>31.34998924708335</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="V26" t="n">
-        <v>720.5656565656566</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="W26" t="n">
-        <v>720.5656565656566</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="X26" t="n">
-        <v>477.1313131313132</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="Y26" t="n">
-        <v>477.1313131313132</v>
+        <v>559.1338160830064</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>900.5394129307539</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C27" t="n">
-        <v>726.0863836496269</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D27" t="n">
-        <v>577.1519739883756</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E27" t="n">
-        <v>417.9145189829202</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F27" t="n">
-        <v>271.3799610098052</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G27" t="n">
-        <v>132.6491355924207</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>486.8199999999999</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N27" t="n">
-        <v>725.41</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>934.7112791079849</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>706.487660844374</v>
       </c>
       <c r="V27" t="n">
-        <v>964</v>
+        <v>471.3355526126313</v>
       </c>
       <c r="W27" t="n">
-        <v>964</v>
+        <v>227.8867759685313</v>
       </c>
       <c r="X27" t="n">
-        <v>964</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y27" t="n">
-        <v>964</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C29" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F29" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W29" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X29" t="n">
-        <v>720.5656565656566</v>
+        <v>749.627473042513</v>
       </c>
       <c r="Y29" t="n">
-        <v>477.1313131313132</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>754.7589876104247</v>
+        <v>343.4227147053767</v>
       </c>
       <c r="C30" t="n">
-        <v>580.3059583292977</v>
+        <v>168.9696854242497</v>
       </c>
       <c r="D30" t="n">
-        <v>431.3715486680464</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E30" t="n">
-        <v>272.1340936625909</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F30" t="n">
-        <v>272.1340936625909</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G30" t="n">
-        <v>133.4032682452064</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N30" t="n">
-        <v>851.7806659261865</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V30" t="n">
-        <v>790.5826554506689</v>
+        <v>962.9383285750775</v>
       </c>
       <c r="W30" t="n">
-        <v>790.5826554506689</v>
+        <v>719.4895519309775</v>
       </c>
       <c r="X30" t="n">
-        <v>790.5826554506689</v>
+        <v>511.6380517254448</v>
       </c>
       <c r="Y30" t="n">
-        <v>790.5826554506689</v>
+        <v>511.6380517254448</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>451.5434343434343</v>
+        <v>333.7844730889342</v>
       </c>
       <c r="C32" t="n">
-        <v>234.3717171717172</v>
+        <v>333.7844730889342</v>
       </c>
       <c r="D32" t="n">
-        <v>234.3717171717172</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E32" t="n">
-        <v>234.3717171717172</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F32" t="n">
-        <v>234.3717171717172</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>22.36462077340309</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>202.4404723580617</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>415.2904723580617</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>621.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>770.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>849.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R32" t="n">
-        <v>849.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S32" t="n">
-        <v>849.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T32" t="n">
-        <v>849.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="U32" t="n">
-        <v>849.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="V32" t="n">
-        <v>849.9083846317729</v>
+        <v>333.7844730889342</v>
       </c>
       <c r="W32" t="n">
-        <v>849.9083846317729</v>
+        <v>333.7844730889342</v>
       </c>
       <c r="X32" t="n">
-        <v>668.7151515151515</v>
+        <v>333.7844730889342</v>
       </c>
       <c r="Y32" t="n">
-        <v>451.5434343434343</v>
+        <v>333.7844730889342</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>44.38772090170167</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C33" t="n">
-        <v>44.38772090170167</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D33" t="n">
-        <v>44.38772090170167</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E33" t="n">
-        <v>44.38772090170167</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F33" t="n">
-        <v>44.38772090170167</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G33" t="n">
-        <v>44.38772090170167</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H33" t="n">
-        <v>44.38772090170167</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I33" t="n">
-        <v>17.95413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>355.4075600578374</v>
+        <v>248.2447175439888</v>
       </c>
       <c r="M33" t="n">
-        <v>568.2575600578374</v>
+        <v>486.8488635328713</v>
       </c>
       <c r="N33" t="n">
-        <v>677.3565223866492</v>
+        <v>725.4530095217538</v>
       </c>
       <c r="O33" t="n">
-        <v>677.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>860</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S33" t="n">
-        <v>686.5826554506689</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T33" t="n">
-        <v>686.5826554506689</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U33" t="n">
-        <v>469.4109382789517</v>
+        <v>423.4027210148092</v>
       </c>
       <c r="V33" t="n">
-        <v>469.4109382789517</v>
+        <v>188.2506127830665</v>
       </c>
       <c r="W33" t="n">
-        <v>252.2392211072345</v>
+        <v>188.2506127830665</v>
       </c>
       <c r="X33" t="n">
-        <v>44.38772090170167</v>
+        <v>188.2506127830665</v>
       </c>
       <c r="Y33" t="n">
-        <v>44.38772090170167</v>
+        <v>188.2506127830665</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q34" t="n">
-        <v>151.7322904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V34" t="n">
-        <v>151.7322904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>849.9083846317729</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R35" t="n">
-        <v>698.5254372164702</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S35" t="n">
-        <v>698.5254372164702</v>
+        <v>650.444607311663</v>
       </c>
       <c r="T35" t="n">
-        <v>698.5254372164702</v>
+        <v>432.8749126823416</v>
       </c>
       <c r="U35" t="n">
-        <v>698.5254372164702</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="V35" t="n">
-        <v>698.5254372164702</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="W35" t="n">
-        <v>698.5254372164702</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="X35" t="n">
-        <v>668.7151515151515</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y35" t="n">
-        <v>451.5434343434343</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>17.2</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="C36" t="n">
-        <v>17.2</v>
+        <v>471.9379424544641</v>
       </c>
       <c r="D36" t="n">
-        <v>17.2</v>
+        <v>323.0035327932128</v>
       </c>
       <c r="E36" t="n">
-        <v>17.2</v>
+        <v>163.7660777877573</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L36" t="n">
-        <v>38.80652238664919</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="M36" t="n">
-        <v>251.6565223866492</v>
+        <v>183.0578391930369</v>
       </c>
       <c r="N36" t="n">
-        <v>464.5065223866492</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="O36" t="n">
-        <v>677.3565223866492</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P36" t="n">
-        <v>860</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="T36" t="n">
-        <v>657.813405358766</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="U36" t="n">
-        <v>451.5434343434343</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="V36" t="n">
-        <v>234.3717171717172</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="W36" t="n">
-        <v>17.2</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="X36" t="n">
-        <v>17.2</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="Y36" t="n">
-        <v>17.2</v>
+        <v>688.1586461827818</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="C37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="D37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="E37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="G37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="H37" t="n">
-        <v>17.2</v>
+        <v>151.763810304913</v>
       </c>
       <c r="I37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K37" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L37" t="n">
-        <v>44.51412500771298</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M37" t="n">
-        <v>83.70216319993516</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N37" t="n">
-        <v>127.3930138553715</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="T37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="U37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="V37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="W37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="X37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Y37" t="n">
-        <v>151.7322904902707</v>
+        <v>151.763810304913</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>425.6565656565656</v>
+        <v>459.4731123480227</v>
       </c>
       <c r="C38" t="n">
-        <v>425.6565656565656</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="D38" t="n">
-        <v>425.6565656565656</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="E38" t="n">
-        <v>208.4848484848484</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="F38" t="n">
-        <v>17.2</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="G38" t="n">
-        <v>17.2</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="H38" t="n">
-        <v>17.2</v>
+        <v>241.9034177187013</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>29.30150906172561</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>120.2150059109224</v>
+        <v>23.55055379931807</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>203.6264053839766</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W38" t="n">
-        <v>860</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="X38" t="n">
-        <v>642.8282828282828</v>
+        <v>459.4731123480227</v>
       </c>
       <c r="Y38" t="n">
-        <v>425.6565656565656</v>
+        <v>459.4731123480227</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.2</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="C39" t="n">
-        <v>17.2</v>
+        <v>471.9379424544641</v>
       </c>
       <c r="D39" t="n">
-        <v>17.2</v>
+        <v>323.0035327932128</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>163.7660777877573</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>142.5575600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>355.4075600578374</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="M39" t="n">
-        <v>568.2575600578374</v>
+        <v>183.0578391930369</v>
       </c>
       <c r="N39" t="n">
-        <v>781.1075600578374</v>
+        <v>396.2978968992348</v>
       </c>
       <c r="O39" t="n">
-        <v>790.6054414866707</v>
+        <v>609.5379546054328</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>792.1814322187836</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S39" t="n">
-        <v>686.5826554506689</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="T39" t="n">
-        <v>686.5826554506689</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="U39" t="n">
-        <v>469.4109382789517</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="V39" t="n">
-        <v>469.4109382789517</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="W39" t="n">
-        <v>432.8117989704867</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="X39" t="n">
-        <v>224.9602987649539</v>
+        <v>646.3909717355911</v>
       </c>
       <c r="Y39" t="n">
-        <v>17.2</v>
+        <v>646.3909717355911</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L40" t="n">
-        <v>752.7818345174422</v>
+        <v>44.54564482235524</v>
       </c>
       <c r="M40" t="n">
-        <v>791.9698727096644</v>
+        <v>83.73368301457742</v>
       </c>
       <c r="N40" t="n">
-        <v>835.6607233651007</v>
+        <v>127.4245336700137</v>
       </c>
       <c r="O40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="P40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="Q40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="R40" t="n">
-        <v>860</v>
+        <v>151.763810304913</v>
       </c>
       <c r="S40" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="T40" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="U40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="V40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y40" t="n">
-        <v>725.4677095097293</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>411.6053543287427</v>
+        <v>445.2559140063055</v>
       </c>
       <c r="C41" t="n">
-        <v>196.4538391772275</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="D41" t="n">
-        <v>17.04</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="E41" t="n">
-        <v>17.04</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>229.6758497463631</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>120.0550059109223</v>
+        <v>120.0889470003098</v>
       </c>
       <c r="L41" t="n">
-        <v>300.1308574955809</v>
+        <v>197.6975058462639</v>
       </c>
       <c r="M41" t="n">
-        <v>511.0008574955809</v>
+        <v>408.9875268274333</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>614.8420490346726</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>764.0369991773207</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>841.9083846317729</v>
+        <v>843.6054391011446</v>
       </c>
       <c r="R41" t="n">
-        <v>841.9083846317729</v>
+        <v>692.2224916858419</v>
       </c>
       <c r="S41" t="n">
-        <v>841.9083846317729</v>
+        <v>692.2224916858419</v>
       </c>
       <c r="T41" t="n">
-        <v>841.9083846317729</v>
+        <v>692.2224916858419</v>
       </c>
       <c r="U41" t="n">
-        <v>841.9083846317729</v>
+        <v>692.2224916858419</v>
       </c>
       <c r="V41" t="n">
-        <v>841.9083846317729</v>
+        <v>692.2224916858419</v>
       </c>
       <c r="W41" t="n">
-        <v>841.9083846317729</v>
+        <v>692.2224916858419</v>
       </c>
       <c r="X41" t="n">
-        <v>841.9083846317729</v>
+        <v>692.2224916858419</v>
       </c>
       <c r="Y41" t="n">
-        <v>626.7568694802578</v>
+        <v>660.8359782662478</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>723.8463836496269</v>
+        <v>321.3673965023727</v>
       </c>
       <c r="C42" t="n">
-        <v>723.8463836496269</v>
+        <v>321.3673965023727</v>
       </c>
       <c r="D42" t="n">
-        <v>574.9119739883756</v>
+        <v>321.3673965023727</v>
       </c>
       <c r="E42" t="n">
-        <v>415.6745189829202</v>
+        <v>321.3673965023727</v>
       </c>
       <c r="F42" t="n">
-        <v>269.1399610098052</v>
+        <v>269.1739020991926</v>
       </c>
       <c r="G42" t="n">
-        <v>130.4091355924207</v>
+        <v>130.4430766818081</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>142.3975600578374</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>353.2675600578374</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>564.1375600578374</v>
+        <v>565.0115431095638</v>
       </c>
       <c r="N42" t="n">
-        <v>775.0075600578374</v>
+        <v>776.3015640907333</v>
       </c>
       <c r="O42" t="n">
-        <v>782.6054414866707</v>
+        <v>776.3015640907333</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="U42" t="n">
-        <v>852</v>
+        <v>752.5275250222574</v>
       </c>
       <c r="V42" t="n">
-        <v>852</v>
+        <v>536.947460762315</v>
       </c>
       <c r="W42" t="n">
-        <v>852</v>
+        <v>321.3673965023727</v>
       </c>
       <c r="X42" t="n">
-        <v>852</v>
+        <v>321.3673965023727</v>
       </c>
       <c r="Y42" t="n">
-        <v>852</v>
+        <v>321.3673965023727</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="S43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="T43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8439,16 +8439,16 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
-        <v>256.1824907047645</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q8" t="n">
         <v>212.3149906599047</v>
@@ -8518,16 +8518,16 @@
         <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>168.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>157.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>168.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>158.9239023638252</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
         <v>139.9817740860215</v>
@@ -8594,16 +8594,16 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812383</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>163.0416663658825</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>135.0065633140411</v>
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M11" t="n">
-        <v>255.2957281767677</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>253.9981915106306</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,25 +8749,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>163.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
-        <v>167.0835288715133</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N12" t="n">
-        <v>131.3417120833333</v>
+        <v>156.9620032779641</v>
       </c>
       <c r="O12" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>159.5946986089611</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>220.0898510449805</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L14" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>256.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>255.0477063711817</v>
+        <v>254.6833393357264</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,22 +8986,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
-        <v>164.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>166.719161836058</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>168.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P15" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>220.0898510449805</v>
+        <v>247.6798763052967</v>
       </c>
       <c r="L17" t="n">
-        <v>262.6351018386741</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M17" t="n">
-        <v>258.3462332272727</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>257.4130635965909</v>
+        <v>255.8883403615408</v>
       </c>
       <c r="O17" t="n">
-        <v>230.0982114216867</v>
+        <v>257.6882366820029</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>258.8230210155857</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9223,22 +9223,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>165.841438974359</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>166.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>170.1340339220183</v>
+        <v>168.6093106869682</v>
       </c>
       <c r="N18" t="n">
-        <v>158.2103989520202</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>133.9744074143302</v>
+        <v>161.5644326746464</v>
       </c>
       <c r="Q18" t="n">
         <v>139.9817740860215</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,13 +9466,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>185.8535934954385</v>
+        <v>185.8815939223662</v>
       </c>
       <c r="P21" t="n">
         <v>133.9744074143302</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,25 +9697,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>382.5729051834858</v>
+        <v>242.4075215744184</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9855,7 +9855,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K26" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
         <v>417.6612145504504</v>
@@ -9940,13 +9940,13 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>255.4868966228399</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P27" t="n">
         <v>133.9744074143302</v>
@@ -10107,7 +10107,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P29" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q29" t="n">
         <v>212.3149906599047</v>
@@ -10177,19 +10177,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>372.3417120833333</v>
+        <v>174.6270615612551</v>
       </c>
       <c r="O30" t="n">
-        <v>255.9491071452661</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R30" t="n">
         <v>45.52166981132082</v>
@@ -10329,13 +10329,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711648</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>445.3462332272727</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N32" t="n">
         <v>437.3469244119842</v>
@@ -10408,22 +10408,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>353.5543797798742</v>
+        <v>369.8307175917693</v>
       </c>
       <c r="M33" t="n">
-        <v>357.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>241.5426841326382</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q33" t="n">
         <v>139.9817740860215</v>
@@ -10566,13 +10566,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
@@ -10645,25 +10645,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K36" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L36" t="n">
-        <v>160.3791498673986</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
-        <v>357.1340339220183</v>
+        <v>183.0115685892478</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>324.1454125711647</v>
+        <v>226.4727136557642</v>
       </c>
       <c r="L38" t="n">
-        <v>318.8224416842694</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10885,19 +10885,19 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>353.5543797798742</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M39" t="n">
-        <v>357.1340339220183</v>
+        <v>183.0115685892478</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O39" t="n">
-        <v>152.1900640695285</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
         <v>210.0772877358491</v>
@@ -11043,13 +11043,13 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L41" t="n">
-        <v>417.6612145504504</v>
+        <v>314.1588986527692</v>
       </c>
       <c r="M41" t="n">
-        <v>443.3462332272727</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
-        <v>332.5889596266112</v>
+        <v>437.3469244119842</v>
       </c>
       <c r="O41" t="n">
         <v>380.8001812627454</v>
@@ -11122,22 +11122,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>355.1340339220183</v>
+        <v>355.5582975393612</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>150.2708721503366</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>212.1516704230558</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -22987,7 +22987,7 @@
         <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
-        <v>355.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
         <v>406.8760457417114</v>
@@ -22999,10 +22999,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>209.5150781395633</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -23023,7 +23023,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
         <v>149.8691179411497</v>
@@ -23041,10 +23041,10 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W8" t="n">
-        <v>323.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X8" t="n">
-        <v>343.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
         <v>386.2379386560536</v>
@@ -23057,10 +23057,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140.5331836498673</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C9" t="n">
-        <v>149.8076989883157</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
         <v>147.4450655646388</v>
@@ -23108,7 +23108,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
-        <v>145.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T9" t="n">
         <v>200.1647286948216</v>
@@ -23120,7 +23120,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>225.6949831609196</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
@@ -23136,7 +23136,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>157.288296313387</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C10" t="n">
         <v>167.2468210986278</v>
@@ -23157,10 +23157,10 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -23187,7 +23187,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S10" t="n">
-        <v>198.0165980369723</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T10" t="n">
         <v>227.9455894282815</v>
@@ -23227,16 +23227,16 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>383.9752457417114</v>
+        <v>384.3096932574806</v>
       </c>
       <c r="G11" t="n">
-        <v>389.302737515135</v>
+        <v>389.6824463205042</v>
       </c>
       <c r="H11" t="n">
-        <v>313.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I11" t="n">
-        <v>184.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J11" t="n">
         <v>11.94928935461252</v>
@@ -23309,13 +23309,13 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G12" t="n">
-        <v>111.3435171632106</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H12" t="n">
-        <v>86.23544423649646</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -23351,16 +23351,16 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>200.321090886344</v>
       </c>
       <c r="V12" t="n">
-        <v>232.8005871494253</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W12" t="n">
-        <v>228.7941831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X12" t="n">
-        <v>205.7729852034775</v>
+        <v>183.2066327192466</v>
       </c>
       <c r="Y12" t="n">
         <v>205.6826957773044</v>
@@ -23379,28 +23379,28 @@
         <v>167.2468210986278</v>
       </c>
       <c r="D13" t="n">
-        <v>148.6154730182124</v>
+        <v>122.9951818235815</v>
       </c>
       <c r="E13" t="n">
         <v>146.4339626465692</v>
       </c>
       <c r="F13" t="n">
-        <v>119.4210480229312</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>141.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H13" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>155.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J13" t="n">
-        <v>93.08498807400534</v>
+        <v>70.79282763244194</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,7 +23418,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R13" t="n">
         <v>177.2933913771695</v>
@@ -23452,10 +23452,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>369.8237408780254</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C14" t="n">
-        <v>339.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D14" t="n">
         <v>354.683041620683</v>
@@ -23467,13 +23467,13 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G14" t="n">
-        <v>415.302737515135</v>
+        <v>392.7363850309042</v>
       </c>
       <c r="H14" t="n">
-        <v>339.4748021157671</v>
+        <v>313.8545109211363</v>
       </c>
       <c r="I14" t="n">
-        <v>210.4758895704059</v>
+        <v>184.8555983757751</v>
       </c>
       <c r="J14" t="n">
         <v>11.94928935461252</v>
@@ -23497,10 +23497,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>123.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S14" t="n">
         <v>209.0200695862453</v>
@@ -23509,7 +23509,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U14" t="n">
-        <v>225.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23546,10 +23546,10 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
-        <v>137.3435171632106</v>
+        <v>114.7771646789798</v>
       </c>
       <c r="H15" t="n">
-        <v>112.2354442364965</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I15" t="n">
         <v>89.39663285141508</v>
@@ -23579,7 +23579,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
         <v>171.6831711038378</v>
@@ -23591,13 +23591,13 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
-        <v>206.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
-        <v>225.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X15" t="n">
-        <v>182.8721852034775</v>
+        <v>180.1526940088467</v>
       </c>
       <c r="Y15" t="n">
         <v>205.6826957773044</v>
@@ -23622,22 +23622,22 @@
         <v>146.4339626465692</v>
       </c>
       <c r="F16" t="n">
-        <v>145.1468559802638</v>
+        <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>141.9909793584588</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>162.2271725074396</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -23655,22 +23655,22 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q16" t="n">
-        <v>86.16204325169439</v>
+        <v>60.54175205706355</v>
       </c>
       <c r="R16" t="n">
         <v>177.2933913771695</v>
       </c>
       <c r="S16" t="n">
-        <v>224.0165980369723</v>
+        <v>198.3963068423414</v>
       </c>
       <c r="T16" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U16" t="n">
-        <v>286.3190293564909</v>
+        <v>260.69873816186</v>
       </c>
       <c r="V16" t="n">
-        <v>252.137643323828</v>
+        <v>229.5712908395972</v>
       </c>
       <c r="W16" t="n">
         <v>286.522998336591</v>
@@ -23692,28 +23692,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C17" t="n">
-        <v>340.6104917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D17" t="n">
-        <v>326.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E17" t="n">
-        <v>353.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>406.8760457417114</v>
+        <v>404.5147400615823</v>
       </c>
       <c r="G17" t="n">
-        <v>387.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>339.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>210.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,7 +23734,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>149.8691179411497</v>
@@ -23786,7 +23786,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H18" t="n">
-        <v>112.2354442364965</v>
+        <v>87.93414998721002</v>
       </c>
       <c r="I18" t="n">
         <v>89.39663285141508</v>
@@ -23816,19 +23816,19 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>147.0207711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>172.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>197.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
-        <v>204.8005871494253</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W18" t="n">
         <v>251.6949831609196</v>
@@ -23850,7 +23850,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C19" t="n">
-        <v>167.2468210986278</v>
+        <v>139.6567958383117</v>
       </c>
       <c r="D19" t="n">
         <v>148.6154730182124</v>
@@ -23862,10 +23862,10 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G19" t="n">
-        <v>145.9685117322726</v>
+        <v>140.4009540981426</v>
       </c>
       <c r="H19" t="n">
-        <v>162.2271725074396</v>
+        <v>139.7784131469302</v>
       </c>
       <c r="I19" t="n">
         <v>155.4504749272583</v>
@@ -23892,19 +23892,19 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q19" t="n">
-        <v>58.16204325169439</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
         <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>196.4265727766561</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U19" t="n">
-        <v>258.3190293564909</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V19" t="n">
         <v>252.137643323828</v>
@@ -23916,7 +23916,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y19" t="n">
-        <v>190.5846533520948</v>
+        <v>218.5846533520948</v>
       </c>
     </row>
     <row r="20">
@@ -23926,19 +23926,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C20" t="n">
-        <v>153.0000917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E20" t="n">
-        <v>140.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
         <v>415.302737515135</v>
@@ -23992,10 +23992,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>369.731100678469</v>
+        <v>157.445715035027</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24005,25 +24005,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>15.10021433385501</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I21" t="n">
         <v>89.39663285141508</v>
@@ -24059,22 +24059,22 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>171.0220216300238</v>
       </c>
     </row>
     <row r="22">
@@ -24093,7 +24093,7 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E22" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120115</v>
       </c>
       <c r="F22" t="n">
         <v>145.4210480229312</v>
@@ -24135,7 +24135,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
@@ -24163,22 +24163,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F23" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>213.0206367296798</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24226,13 +24226,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W23" t="n">
-        <v>349.240968717413</v>
+        <v>146.9462822885158</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="24">
@@ -24245,7 +24245,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
@@ -24257,7 +24257,7 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>32.66058619227026</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
         <v>112.2354442364965</v>
@@ -24266,7 +24266,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24293,7 +24293,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -24302,16 +24302,16 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
         <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>205.7729852034775</v>
+        <v>75.68862979473269</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -24330,13 +24330,13 @@
         <v>148.6154730182124</v>
       </c>
       <c r="E25" t="n">
-        <v>146.4339626465692</v>
+        <v>13.24699506120115</v>
       </c>
       <c r="F25" t="n">
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>120.9660550247851</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24366,7 +24366,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R25" t="n">
         <v>177.2933913771695</v>
@@ -24400,19 +24400,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>182.4103310180931</v>
+        <v>342.2575625303454</v>
       </c>
       <c r="C26" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D26" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
         <v>415.302737515135</v>
@@ -24445,10 +24445,10 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
@@ -24460,13 +24460,13 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y26" t="n">
         <v>386.2379386560536</v>
@@ -24479,31 +24479,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>103.7072024513137</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -24533,19 +24533,19 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
-        <v>200.1647286948216</v>
+        <v>171.1123110561968</v>
       </c>
       <c r="U27" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
         <v>205.6826957773044</v>
@@ -24618,10 +24618,10 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V28" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>170.4610416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D29" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E29" t="n">
         <v>381.9303700722618</v>
@@ -24652,7 +24652,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
         <v>339.4748021157671</v>
@@ -24697,16 +24697,16 @@
         <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>327.7522584701349</v>
+        <v>115.4668728266929</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X29" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="30">
@@ -24716,7 +24716,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>131.0677524880256</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -24725,16 +24725,16 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
         <v>89.39663285141508</v>
@@ -24767,7 +24767,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T30" t="n">
         <v>200.1647286948216</v>
@@ -24776,13 +24776,13 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
-        <v>232.8005871494253</v>
+        <v>231.6929484832222</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
         <v>205.6826957773044</v>
@@ -24822,7 +24822,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -24840,7 +24840,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R31" t="n">
         <v>177.2933913771695</v>
@@ -24852,7 +24852,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
-        <v>261.5635968487001</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="32">
@@ -24877,10 +24877,10 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C32" t="n">
-        <v>150.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D32" t="n">
-        <v>354.683041620683</v>
+        <v>284.3390338194077</v>
       </c>
       <c r="E32" t="n">
         <v>381.9303700722618</v>
@@ -24889,10 +24889,10 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H32" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I32" t="n">
         <v>210.4758895704059</v>
@@ -24922,28 +24922,28 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
-        <v>190.3497998930139</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="33">
@@ -24953,7 +24953,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>172.7084989883157</v>
@@ -24974,7 +24974,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I33" t="n">
-        <v>63.22738048498828</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -25001,25 +25001,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>10.94138208097482</v>
+        <v>162.6992258814087</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
         <v>205.6826957773044</v>
@@ -25080,7 +25080,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S34" t="n">
         <v>224.0165980369723</v>
@@ -25095,7 +25095,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25111,7 +25111,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>167.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
         <v>365.2728917710076</v>
@@ -25126,7 +25126,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25156,19 +25156,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S35" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>223.0958495641314</v>
+        <v>7.701851881103124</v>
       </c>
       <c r="U35" t="n">
-        <v>251.3456529078365</v>
+        <v>55.25269165184244</v>
       </c>
       <c r="V35" t="n">
         <v>327.7522584701349</v>
@@ -25177,10 +25177,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
-        <v>340.2189178341636</v>
+        <v>154.3371029954408</v>
       </c>
       <c r="Y35" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25190,19 +25190,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>125.1831859471485</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -25241,19 +25241,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>21.73411077579652</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
-        <v>17.80058714942527</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>36.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
@@ -25272,7 +25272,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C37" t="n">
-        <v>34.05985351325981</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D37" t="n">
         <v>148.6154730182124</v>
@@ -25290,7 +25290,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I37" t="n">
-        <v>155.4504749272583</v>
+        <v>22.26350734189026</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
@@ -25351,16 +25351,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>365.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>217.5040457417115</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
@@ -25369,10 +25369,10 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25411,13 +25411,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W38" t="n">
-        <v>349.240968717413</v>
+        <v>133.8469710343848</v>
       </c>
       <c r="X38" t="n">
-        <v>154.731100678469</v>
+        <v>187.043248761248</v>
       </c>
       <c r="Y38" t="n">
-        <v>171.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="39">
@@ -25430,16 +25430,16 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>137.3435171632106</v>
@@ -25475,28 +25475,28 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>58.80783644992434</v>
       </c>
       <c r="T39" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V39" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>215.4618352455393</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25557,13 +25557,13 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S40" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T40" t="n">
         <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,13 +25585,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>169.3095780461377</v>
       </c>
       <c r="C41" t="n">
-        <v>152.2728917710076</v>
+        <v>151.8486281536646</v>
       </c>
       <c r="D41" t="n">
-        <v>177.0633408352277</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E41" t="n">
         <v>381.9303700722618</v>
@@ -25606,7 +25606,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I41" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>11.94928935461252</v>
@@ -25633,7 +25633,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>209.0200695862453</v>
@@ -25654,7 +25654,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>173.2379386560536</v>
+        <v>355.1652903706555</v>
       </c>
     </row>
     <row r="42">
@@ -25664,19 +25664,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39.66110346299797</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>93.39765293423562</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -25712,7 +25712,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>171.6831711038378</v>
@@ -25724,10 +25724,10 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>19.37632353208235</v>
       </c>
       <c r="W42" t="n">
-        <v>251.6949831609196</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350387.4464706169</v>
+        <v>327897.5868709115</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350387.4464706169</v>
+        <v>350071.9014065735</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350387.4464706169</v>
+        <v>350071.9014065734</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>352034.7526374221</v>
+        <v>351708.7869702388</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>507077.4418798315</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>507077.4418798315</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>507077.4418798316</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>507077.4418798316</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488273.6054418518</v>
+        <v>507087.7759459231</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488273.6054418518</v>
+        <v>488558.5542106443</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488273.6054418518</v>
+        <v>488558.5542106444</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486827.1564850841</v>
+        <v>487133.9943184342</v>
       </c>
     </row>
     <row r="16">
@@ -26264,43 +26264,43 @@
         <v>75255.18387201249</v>
       </c>
       <c r="C2" t="n">
-        <v>75255.18387201248</v>
+        <v>75255.18387201249</v>
       </c>
       <c r="D2" t="n">
-        <v>80408.21497650829</v>
+        <v>75255.18387201249</v>
       </c>
       <c r="E2" t="n">
-        <v>80408.2149765083</v>
+        <v>80335.91512409358</v>
       </c>
       <c r="F2" t="n">
-        <v>80408.2149765083</v>
+        <v>80335.91512409358</v>
       </c>
       <c r="G2" t="n">
-        <v>80785.65708007243</v>
+        <v>80710.96958749177</v>
       </c>
       <c r="H2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="I2" t="n">
-        <v>116310.1029597295</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="J2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="K2" t="n">
-        <v>116310.1029597296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="L2" t="n">
-        <v>112001.6387997296</v>
+        <v>116312.4707719327</v>
       </c>
       <c r="M2" t="n">
-        <v>112001.6387997296</v>
+        <v>112066.9282188238</v>
       </c>
       <c r="N2" t="n">
-        <v>112001.6387997295</v>
+        <v>112066.9282188238</v>
       </c>
       <c r="O2" t="n">
-        <v>111670.2184797295</v>
+        <v>111740.5232716417</v>
       </c>
       <c r="P2" t="n">
         <v>75255.18387201249</v>
@@ -26319,19 +26319,19 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>7649.655304310485</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26876.8513828616</v>
+        <v>27190.2942010693</v>
       </c>
       <c r="C4" t="n">
-        <v>26876.8513828616</v>
+        <v>27190.2942010693</v>
       </c>
       <c r="D4" t="n">
-        <v>28777.11938676419</v>
+        <v>27190.2942010693</v>
       </c>
       <c r="E4" t="n">
-        <v>28777.11938676419</v>
+        <v>29085.49165026514</v>
       </c>
       <c r="F4" t="n">
-        <v>28777.11938676419</v>
+        <v>29085.49165026514</v>
       </c>
       <c r="G4" t="n">
-        <v>28916.30759234339</v>
+        <v>29225.39321700331</v>
       </c>
       <c r="H4" t="n">
-        <v>42016.55218480954</v>
+        <v>42505.34661045596</v>
       </c>
       <c r="I4" t="n">
-        <v>42016.55218480954</v>
+        <v>42505.34661045596</v>
       </c>
       <c r="J4" t="n">
-        <v>42016.55218480955</v>
+        <v>42505.34661045596</v>
       </c>
       <c r="K4" t="n">
-        <v>42016.55218480954</v>
+        <v>42505.34661045596</v>
       </c>
       <c r="L4" t="n">
-        <v>40427.73262925399</v>
+        <v>42505.34661045596</v>
       </c>
       <c r="M4" t="n">
-        <v>40427.73262925399</v>
+        <v>40921.68846797723</v>
       </c>
       <c r="N4" t="n">
-        <v>40427.73262925399</v>
+        <v>40921.68846797723</v>
       </c>
       <c r="O4" t="n">
-        <v>40305.5157403651</v>
+        <v>40799.9339817404</v>
       </c>
       <c r="P4" t="n">
-        <v>26876.8513828616</v>
+        <v>27190.2942010693</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>33627.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.7324891509</v>
+        <v>14437.2896709432</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915088</v>
+        <v>14437.2896709432</v>
       </c>
       <c r="D6" t="n">
-        <v>8346.315589744096</v>
+        <v>14437.2896709432</v>
       </c>
       <c r="E6" t="n">
-        <v>50050.29558974411</v>
+        <v>42043.05446488439</v>
       </c>
       <c r="F6" t="n">
-        <v>50050.29558974411</v>
+        <v>49692.70976919487</v>
       </c>
       <c r="G6" t="n">
-        <v>49618.77948772904</v>
+        <v>49268.22827326787</v>
       </c>
       <c r="H6" t="n">
-        <v>2171.433774920039</v>
+        <v>1569.66825538336</v>
       </c>
       <c r="I6" t="n">
-        <v>59640.75077492</v>
+        <v>59153.45539771504</v>
       </c>
       <c r="J6" t="n">
-        <v>59640.75077492003</v>
+        <v>59153.45539771506</v>
       </c>
       <c r="K6" t="n">
-        <v>59640.75077492003</v>
+        <v>59153.45539771506</v>
       </c>
       <c r="L6" t="n">
-        <v>58501.90617047557</v>
+        <v>59153.45539771504</v>
       </c>
       <c r="M6" t="n">
-        <v>58501.90617047559</v>
+        <v>58049.28469171848</v>
       </c>
       <c r="N6" t="n">
-        <v>58501.90617047554</v>
+        <v>58049.28469171847</v>
       </c>
       <c r="O6" t="n">
-        <v>58414.30273936444</v>
+        <v>57964.39406196681</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.3324891509</v>
+        <v>48064.8896709432</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26895,7 +26895,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -26904,37 +26904,37 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,49 +26944,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,19 +27191,19 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35094,16 +35094,16 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35173,16 +35173,16 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35249,16 +35249,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24.58512791403967</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -35325,22 +35325,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,25 +35404,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>24.94949494949495</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,22 +35641,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949496</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="L17" t="n">
-        <v>26.86868686868687</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35878,22 +35878,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>28</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N18" t="n">
-        <v>26.86868686868686</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,13 +36121,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>43.25734905099405</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,25 +36352,25 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>239.9766607390413</v>
+        <v>99.8112771299739</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36510,7 +36510,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L26" t="n">
         <v>181.8947995804632</v>
@@ -36595,13 +36595,13 @@
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>113.3528627008216</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -36753,7 +36753,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
-        <v>219.1673002655598</v>
+        <v>219.1673002655597</v>
       </c>
       <c r="N29" t="n">
         <v>207.9338608153932</v>
@@ -36762,7 +36762,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P29" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36832,19 +36832,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>241</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="O30" t="n">
-        <v>113.3528627008217</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -36984,13 +36984,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>215</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N32" t="n">
         <v>207.9338608153932</v>
@@ -37063,22 +37063,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>215</v>
+        <v>231.276337811895</v>
       </c>
       <c r="M33" t="n">
-        <v>215</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>110.2009720493049</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37221,13 +37221,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
@@ -37300,25 +37300,25 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L36" t="n">
-        <v>21.82477008752444</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>215</v>
+        <v>40.87753466722953</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>104.0555615261842</v>
+        <v>6.382862610783645</v>
       </c>
       <c r="L38" t="n">
-        <v>83.05602671428214</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37540,19 +37540,19 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>215</v>
+        <v>40.87753466722953</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O39" t="n">
-        <v>9.59381962508408</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
         <v>70.09551364982758</v>
@@ -37698,13 +37698,13 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L41" t="n">
-        <v>181.8947995804632</v>
+        <v>78.39248368278189</v>
       </c>
       <c r="M41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
-        <v>103.1758960300203</v>
+        <v>207.9338608153932</v>
       </c>
       <c r="O41" t="n">
         <v>150.7019698410586</v>
@@ -37777,22 +37777,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>7.674627705892183</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>78.17726300872559</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
